--- a/R_Codes/DataSummary/Archaea/Sample_name/Archaea_Summary_Order_by_Sample_name.xlsx
+++ b/R_Codes/DataSummary/Archaea/Sample_name/Archaea_Summary_Order_by_Sample_name.xlsx
@@ -481,10 +481,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>37.5918082071325</v>
+        <v>37.6083286086558</v>
       </c>
       <c r="D2" t="n">
-        <v>5.59724283853563</v>
+        <v>5.60163716781323</v>
       </c>
     </row>
     <row r="3">
@@ -495,10 +495,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>19.2288487135942</v>
+        <v>19.218471533848</v>
       </c>
       <c r="D3" t="n">
-        <v>2.24433712249579</v>
+        <v>2.2429594916445</v>
       </c>
     </row>
     <row r="4">
@@ -509,10 +509,10 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>8.83085837103093</v>
+        <v>8.83030019633991</v>
       </c>
       <c r="D4" t="n">
-        <v>1.18874316365223</v>
+        <v>1.18860523810051</v>
       </c>
     </row>
     <row r="5">
@@ -523,10 +523,10 @@
         <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>8.09463516172468</v>
+        <v>8.09618084032267</v>
       </c>
       <c r="D5" t="n">
-        <v>1.77500895016411</v>
+        <v>1.77463760386218</v>
       </c>
     </row>
     <row r="6">
@@ -537,10 +537,10 @@
         <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>6.13446469182453</v>
+        <v>6.13136091759335</v>
       </c>
       <c r="D6" t="n">
-        <v>0.291996804378204</v>
+        <v>0.29173508235607</v>
       </c>
     </row>
     <row r="7">
@@ -551,10 +551,10 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>5.68760810180059</v>
+        <v>5.68487064359714</v>
       </c>
       <c r="D7" t="n">
-        <v>0.202215927141487</v>
+        <v>0.202040563636338</v>
       </c>
     </row>
     <row r="8">
@@ -565,10 +565,10 @@
         <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>4.26967222633716</v>
+        <v>4.26749999551657</v>
       </c>
       <c r="D8" t="n">
-        <v>0.136065425139798</v>
+        <v>0.136006692264525</v>
       </c>
     </row>
     <row r="9">
@@ -579,10 +579,10 @@
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>3.82594060539674</v>
+        <v>3.8253130345831</v>
       </c>
       <c r="D9" t="n">
-        <v>0.262571455915814</v>
+        <v>0.262482563188048</v>
       </c>
     </row>
     <row r="10">
@@ -593,10 +593,10 @@
         <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>1.614157665827</v>
+        <v>1.61344272707602</v>
       </c>
       <c r="D10" t="n">
-        <v>0.789400869514276</v>
+        <v>0.789053066778589</v>
       </c>
     </row>
     <row r="11">
@@ -607,10 +607,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>1.60491681905068</v>
+        <v>1.60475341957924</v>
       </c>
       <c r="D11" t="n">
-        <v>0.203347398935847</v>
+        <v>0.203320697582051</v>
       </c>
     </row>
     <row r="12">
@@ -621,10 +621,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>1.37355874984232</v>
+        <v>1.37632070583837</v>
       </c>
       <c r="D12" t="n">
-        <v>0.608027825036764</v>
+        <v>0.609441380320974</v>
       </c>
     </row>
     <row r="13">
@@ -635,10 +635,10 @@
         <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>0.477247905242917</v>
+        <v>0.477051715520837</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0450023147999319</v>
+        <v>0.0449831141801297</v>
       </c>
     </row>
     <row r="14">
@@ -649,7 +649,7 @@
         <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>0.476758293076138</v>
+        <v>0.476429470271012</v>
       </c>
       <c r="D14"/>
     </row>
@@ -661,10 +661,10 @@
         <v>18</v>
       </c>
       <c r="C15" t="n">
-        <v>0.270575615186224</v>
+        <v>0.270468621631591</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0205268698885638</v>
+        <v>0.0205094904998427</v>
       </c>
     </row>
     <row r="16">
@@ -675,7 +675,7 @@
         <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>0.115689526293467</v>
+        <v>0.115783032995387</v>
       </c>
       <c r="D16"/>
     </row>
@@ -687,10 +687,10 @@
         <v>20</v>
       </c>
       <c r="C17" t="n">
-        <v>0.10336839725838</v>
+        <v>0.10349339817975</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0254780013641728</v>
+        <v>0.0254968433941032</v>
       </c>
     </row>
     <row r="18">
@@ -701,10 +701,10 @@
         <v>21</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0991157658669333</v>
+        <v>0.0991442804136611</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0174851506219885</v>
+        <v>0.0174930856340913</v>
       </c>
     </row>
     <row r="19">
@@ -715,10 +715,10 @@
         <v>22</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0836277009911762</v>
+        <v>0.0836599616266827</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0227641652334727</v>
+        <v>0.0227635062895201</v>
       </c>
     </row>
     <row r="20">
@@ -729,10 +729,10 @@
         <v>23</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0433672033818553</v>
+        <v>0.0433731723234349</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0104592563889992</v>
+        <v>0.0104501524378753</v>
       </c>
     </row>
     <row r="21">
@@ -743,7 +743,7 @@
         <v>24</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0313025378626997</v>
+        <v>0.0312869414447345</v>
       </c>
       <c r="D21"/>
     </row>
@@ -755,7 +755,7 @@
         <v>25</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0130089175550854</v>
+        <v>0.0129953377876777</v>
       </c>
       <c r="D22"/>
     </row>
@@ -767,7 +767,7 @@
         <v>26</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0115462983521061</v>
+        <v>0.0115447261229262</v>
       </c>
       <c r="D23"/>
     </row>
@@ -779,7 +779,7 @@
         <v>27</v>
       </c>
       <c r="C24" t="n">
-        <v>0.00982099833583932</v>
+        <v>0.00983170785250912</v>
       </c>
       <c r="D24"/>
     </row>
@@ -791,7 +791,7 @@
         <v>28</v>
       </c>
       <c r="C25" t="n">
-        <v>0.00632532289747537</v>
+        <v>0.00631872001038943</v>
       </c>
       <c r="D25"/>
     </row>
@@ -803,7 +803,7 @@
         <v>29</v>
       </c>
       <c r="C26" t="n">
-        <v>0.00177620413836834</v>
+        <v>0.00177629086912041</v>
       </c>
       <c r="D26"/>
     </row>
@@ -840,10 +840,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>59.7972040101877</v>
+        <v>60.0117510250063</v>
       </c>
       <c r="D2" t="n">
-        <v>18.976589310687</v>
+        <v>19.0438950283452</v>
       </c>
     </row>
     <row r="3">
@@ -854,10 +854,10 @@
         <v>18</v>
       </c>
       <c r="C3" t="n">
-        <v>32.1764152523528</v>
+        <v>32.072524514091</v>
       </c>
       <c r="D3" t="n">
-        <v>0.326105319199372</v>
+        <v>0.324979573100751</v>
       </c>
     </row>
     <row r="4">
@@ -868,10 +868,10 @@
         <v>31</v>
       </c>
       <c r="C4" t="n">
-        <v>1.93891184712223</v>
+        <v>1.93261553258066</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0663761273090235</v>
+        <v>0.0661212506766528</v>
       </c>
     </row>
     <row r="5">
@@ -882,10 +882,10 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>1.73075091445215</v>
+        <v>1.72381281041984</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0592720139891462</v>
+        <v>0.0588899026502082</v>
       </c>
     </row>
     <row r="6">
@@ -896,10 +896,10 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>1.08440498494746</v>
+        <v>1.0256963259798</v>
       </c>
       <c r="D6" t="n">
-        <v>0.346796377127552</v>
+        <v>0.326196478513884</v>
       </c>
     </row>
     <row r="7">
@@ -907,13 +907,13 @@
         <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C7" t="n">
-        <v>0.918635764339107</v>
+        <v>0.910475120792083</v>
       </c>
       <c r="D7" t="n">
-        <v>0.160565559093251</v>
+        <v>0.0830873994578001</v>
       </c>
     </row>
     <row r="8">
@@ -921,13 +921,13 @@
         <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>0.913238333415153</v>
+        <v>0.888043173298091</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0833513441043682</v>
+        <v>0.15131718509958</v>
       </c>
     </row>
     <row r="9">
@@ -938,10 +938,10 @@
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>0.467429336718295</v>
+        <v>0.466221221516168</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0165814334542619</v>
+        <v>0.0165396320360491</v>
       </c>
     </row>
     <row r="10">
@@ -952,10 +952,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>0.402296245812782</v>
+        <v>0.401484811843114</v>
       </c>
       <c r="D10" t="n">
-        <v>0.274871069987508</v>
+        <v>0.274321679413749</v>
       </c>
     </row>
     <row r="11">
@@ -966,10 +966,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>0.238905071421871</v>
+        <v>0.238795680159351</v>
       </c>
       <c r="D11" t="n">
-        <v>0.166646810861579</v>
+        <v>0.166575165597134</v>
       </c>
     </row>
     <row r="12">
@@ -980,10 +980,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>0.132284452778502</v>
+        <v>0.13250593027904</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0278585800252594</v>
+        <v>0.0279680233633284</v>
       </c>
     </row>
     <row r="13">
@@ -994,10 +994,10 @@
         <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>0.108520301484974</v>
+        <v>0.105343591806292</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0146072490474575</v>
+        <v>0.0136460636697803</v>
       </c>
     </row>
     <row r="14">
@@ -1008,10 +1008,10 @@
         <v>10</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0412645232350904</v>
+        <v>0.0411239945214958</v>
       </c>
       <c r="D14" t="n">
-        <v>0.00249339953905765</v>
+        <v>0.00248507425191541</v>
       </c>
     </row>
     <row r="15">
@@ -1022,10 +1022,10 @@
         <v>32</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0151854301157901</v>
+        <v>0.015146783271896</v>
       </c>
       <c r="D15" t="n">
-        <v>0.00296997966832071</v>
+        <v>0.00296250525510009</v>
       </c>
     </row>
     <row r="16">
@@ -1036,7 +1036,7 @@
         <v>26</v>
       </c>
       <c r="C16" t="n">
-        <v>0.00743107690211342</v>
+        <v>0.00741230379725906</v>
       </c>
       <c r="D16"/>
     </row>
@@ -1048,10 +1048,10 @@
         <v>13</v>
       </c>
       <c r="C17" t="n">
-        <v>0.00676741122361874</v>
+        <v>0.0067439889623678</v>
       </c>
       <c r="D17" t="n">
-        <v>0.00285785858713188</v>
+        <v>0.00284210346859634</v>
       </c>
     </row>
     <row r="18">
@@ -1062,7 +1062,7 @@
         <v>20</v>
       </c>
       <c r="C18" t="n">
-        <v>0.00613877383033067</v>
+        <v>0.00612320169641204</v>
       </c>
       <c r="D18"/>
     </row>
@@ -1074,7 +1074,7 @@
         <v>21</v>
       </c>
       <c r="C19" t="n">
-        <v>0.00452332814272972</v>
+        <v>0.00451179078774197</v>
       </c>
       <c r="D19"/>
     </row>
@@ -1086,7 +1086,7 @@
         <v>33</v>
       </c>
       <c r="C20" t="n">
-        <v>0.00452332814272972</v>
+        <v>0.00451179078774197</v>
       </c>
       <c r="D20"/>
     </row>
@@ -1098,7 +1098,7 @@
         <v>24</v>
       </c>
       <c r="C21" t="n">
-        <v>0.00387717660683835</v>
+        <v>0.00386730630254106</v>
       </c>
       <c r="D21"/>
     </row>
@@ -1110,7 +1110,7 @@
         <v>34</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0012924367675278</v>
+        <v>0.00128910210084702</v>
       </c>
       <c r="D22"/>
     </row>
@@ -1147,10 +1147,10 @@
         <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>18.5202533685736</v>
+        <v>18.5201013097571</v>
       </c>
       <c r="D2" t="n">
-        <v>0.505976770488784</v>
+        <v>0.505976909932865</v>
       </c>
     </row>
     <row r="3">
@@ -1161,10 +1161,10 @@
         <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>16.5372588192262</v>
+        <v>16.5329845316454</v>
       </c>
       <c r="D3" t="n">
-        <v>3.04154912689679</v>
+        <v>3.04051963402742</v>
       </c>
     </row>
     <row r="4">
@@ -1175,10 +1175,10 @@
         <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>12.4378584460888</v>
+        <v>12.4382553298214</v>
       </c>
       <c r="D4" t="n">
-        <v>0.428313229449437</v>
+        <v>0.428325745678215</v>
       </c>
     </row>
     <row r="5">
@@ -1189,10 +1189,10 @@
         <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>12.3021921641972</v>
+        <v>12.3026594588541</v>
       </c>
       <c r="D5" t="n">
-        <v>0.680026350575475</v>
+        <v>0.680014840542453</v>
       </c>
     </row>
     <row r="6">
@@ -1203,10 +1203,10 @@
         <v>14</v>
       </c>
       <c r="C6" t="n">
-        <v>11.7452341318612</v>
+        <v>11.7458348323098</v>
       </c>
       <c r="D6" t="n">
-        <v>1.37682566368649</v>
+        <v>1.37689345146925</v>
       </c>
     </row>
     <row r="7">
@@ -1217,10 +1217,10 @@
         <v>8</v>
       </c>
       <c r="C7" t="n">
-        <v>6.25422579699541</v>
+        <v>6.25509725438493</v>
       </c>
       <c r="D7" t="n">
-        <v>3.99436845805551</v>
+        <v>3.99503421260845</v>
       </c>
     </row>
     <row r="8">
@@ -1231,10 +1231,10 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>5.47371315766783</v>
+        <v>5.47426332536916</v>
       </c>
       <c r="D8" t="n">
-        <v>0.725016650401825</v>
+        <v>0.725104134642925</v>
       </c>
     </row>
     <row r="9">
@@ -1245,10 +1245,10 @@
         <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>3.83852280450956</v>
+        <v>3.83946933329157</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0622087400615458</v>
+        <v>0.062235005592485</v>
       </c>
     </row>
     <row r="10">
@@ -1259,10 +1259,10 @@
         <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>3.11433185157042</v>
+        <v>3.11454051303145</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0384232790596677</v>
+        <v>0.0384252193784699</v>
       </c>
     </row>
     <row r="11">
@@ -1273,10 +1273,10 @@
         <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>2.19994636630155</v>
+        <v>2.1998961256231</v>
       </c>
       <c r="D11" t="n">
-        <v>0.107160564694792</v>
+        <v>0.107160590329108</v>
       </c>
     </row>
     <row r="12">
@@ -1287,10 +1287,10 @@
         <v>21</v>
       </c>
       <c r="C12" t="n">
-        <v>1.46754394593324</v>
+        <v>1.46756821441988</v>
       </c>
       <c r="D12" t="n">
-        <v>0.221908676469357</v>
+        <v>0.221914596352504</v>
       </c>
     </row>
     <row r="13">
@@ -1301,10 +1301,10 @@
         <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>1.46564892526542</v>
+        <v>1.46612663342029</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0466877372539877</v>
+        <v>0.0467043258433747</v>
       </c>
     </row>
     <row r="14">
@@ -1315,10 +1315,10 @@
         <v>20</v>
       </c>
       <c r="C14" t="n">
-        <v>0.939262261327925</v>
+        <v>0.939235706664847</v>
       </c>
       <c r="D14" t="n">
-        <v>0.076588972054449</v>
+        <v>0.0765853287362225</v>
       </c>
     </row>
     <row r="15">
@@ -1329,10 +1329,10 @@
         <v>22</v>
       </c>
       <c r="C15" t="n">
-        <v>0.922485621046044</v>
+        <v>0.922428448465171</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0956601710709274</v>
+        <v>0.0956434026846114</v>
       </c>
     </row>
     <row r="16">
@@ -1343,10 +1343,10 @@
         <v>32</v>
       </c>
       <c r="C16" t="n">
-        <v>0.702726037156627</v>
+        <v>0.702697770525482</v>
       </c>
       <c r="D16" t="n">
-        <v>0.187953862659956</v>
+        <v>0.187943863450388</v>
       </c>
     </row>
     <row r="17">
@@ -1357,10 +1357,10 @@
         <v>23</v>
       </c>
       <c r="C17" t="n">
-        <v>0.642172015204204</v>
+        <v>0.642169123069737</v>
       </c>
       <c r="D17" t="n">
-        <v>0.165207216080162</v>
+        <v>0.165199823432465</v>
       </c>
     </row>
     <row r="18">
@@ -1371,10 +1371,10 @@
         <v>13</v>
       </c>
       <c r="C18" t="n">
-        <v>0.373053088548069</v>
+        <v>0.373104243580127</v>
       </c>
       <c r="D18" t="n">
-        <v>0.115024472265287</v>
+        <v>0.115042827780335</v>
       </c>
     </row>
     <row r="19">
@@ -1385,10 +1385,10 @@
         <v>24</v>
       </c>
       <c r="C19" t="n">
-        <v>0.242175367283282</v>
+        <v>0.242160708289927</v>
       </c>
       <c r="D19" t="n">
-        <v>0.105117748515762</v>
+        <v>0.105102080516384</v>
       </c>
     </row>
     <row r="20">
@@ -1399,7 +1399,7 @@
         <v>36</v>
       </c>
       <c r="C20" t="n">
-        <v>0.212351047265552</v>
+        <v>0.212345660707166</v>
       </c>
       <c r="D20"/>
     </row>
@@ -1411,10 +1411,10 @@
         <v>27</v>
       </c>
       <c r="C21" t="n">
-        <v>0.140690285136584</v>
+        <v>0.140685141227975</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0128404769835274</v>
+        <v>0.0128378141578971</v>
       </c>
     </row>
     <row r="22">
@@ -1425,10 +1425,10 @@
         <v>31</v>
       </c>
       <c r="C22" t="n">
-        <v>0.139326797297523</v>
+        <v>0.139357882061933</v>
       </c>
       <c r="D22" t="n">
-        <v>0.00657364646947169</v>
+        <v>0.00657574523047377</v>
       </c>
     </row>
     <row r="23">
@@ -1439,10 +1439,10 @@
         <v>19</v>
       </c>
       <c r="C23" t="n">
-        <v>0.114960544008385</v>
+        <v>0.114961862604409</v>
       </c>
       <c r="D23" t="n">
-        <v>0.032622598907635</v>
+        <v>0.0326241618178361</v>
       </c>
     </row>
     <row r="24">
@@ -1453,10 +1453,10 @@
         <v>28</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0757661709457359</v>
+        <v>0.0757499067335201</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0524181217803904</v>
+        <v>0.0524055170092779</v>
       </c>
     </row>
     <row r="25">
@@ -1467,7 +1467,7 @@
         <v>17</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0730903125241704</v>
+        <v>0.0730940892896911</v>
       </c>
       <c r="D25"/>
     </row>
@@ -1479,7 +1479,7 @@
         <v>33</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0301708776892948</v>
+        <v>0.0301647251607637</v>
       </c>
       <c r="D26"/>
     </row>
@@ -1491,7 +1491,7 @@
         <v>15</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0230510669255519</v>
+        <v>0.0230564187299055</v>
       </c>
       <c r="D27"/>
     </row>
@@ -1503,10 +1503,10 @@
         <v>26</v>
       </c>
       <c r="C28" t="n">
-        <v>0.00727727790575996</v>
+        <v>0.00727632488319893</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0014999434261184</v>
+        <v>0.00149874617041298</v>
       </c>
     </row>
     <row r="29">
@@ -1517,7 +1517,7 @@
         <v>37</v>
       </c>
       <c r="C29" t="n">
-        <v>0.00252748841842708</v>
+        <v>0.00252893753007687</v>
       </c>
       <c r="D29"/>
     </row>
@@ -1529,7 +1529,7 @@
         <v>38</v>
       </c>
       <c r="C30" t="n">
-        <v>0.00218396312648901</v>
+        <v>0.00218618854804676</v>
       </c>
       <c r="D30"/>
     </row>
